--- a/xk/output/Q4_最终方案.xlsx
+++ b/xk/output/Q4_最终方案.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>460.7</v>
+        <v>459</v>
       </c>
       <c r="E7" t="n">
-        <v>462.2</v>
+        <v>460.5</v>
       </c>
       <c r="F7" t="n">
-        <v>5.023</v>
+        <v>6.074</v>
       </c>
       <c r="G7" t="n">
-        <v>0.592</v>
+        <v>0.496</v>
       </c>
       <c r="H7" t="n">
-        <v>0.299</v>
+        <v>0.253</v>
       </c>
     </row>
     <row r="8">
@@ -644,7 +644,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>463.2</v>
+        <v>461.7</v>
       </c>
       <c r="E8" t="n">
-        <v>463.7</v>
+        <v>462.2</v>
       </c>
       <c r="F8" t="n">
-        <v>30.394</v>
+        <v>11.076</v>
       </c>
       <c r="G8" t="n">
-        <v>0.054</v>
+        <v>0.592</v>
       </c>
       <c r="H8" t="n">
-        <v>0.492</v>
+        <v>0.299</v>
       </c>
     </row>
     <row r="9">
@@ -674,7 +674,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P17</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -683,19 +683,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>466.8</v>
+        <v>463.2</v>
       </c>
       <c r="E9" t="n">
-        <v>467.3</v>
+        <v>463.7</v>
       </c>
       <c r="F9" t="n">
-        <v>28.037</v>
+        <v>30.394</v>
       </c>
       <c r="G9" t="n">
-        <v>0.051</v>
+        <v>0.054</v>
       </c>
       <c r="H9" t="n">
-        <v>0.706</v>
+        <v>0.492</v>
       </c>
     </row>
     <row r="10">
@@ -704,28 +704,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>468.1</v>
+        <v>464.9</v>
       </c>
       <c r="E10" t="n">
-        <v>469.6</v>
+        <v>465.4</v>
       </c>
       <c r="F10" t="n">
-        <v>27.972</v>
+        <v>11.053</v>
       </c>
       <c r="G10" t="n">
-        <v>1.976</v>
+        <v>0.538</v>
       </c>
       <c r="H10" t="n">
-        <v>0.54</v>
+        <v>0.227</v>
       </c>
     </row>
     <row r="11">
@@ -734,28 +734,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S04</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>477</v>
+        <v>466.8</v>
       </c>
       <c r="E11" t="n">
-        <v>478.5</v>
+        <v>467.3</v>
       </c>
       <c r="F11" t="n">
-        <v>8.241</v>
+        <v>28.037</v>
       </c>
       <c r="G11" t="n">
-        <v>1.63</v>
+        <v>0.051</v>
       </c>
       <c r="H11" t="n">
-        <v>0.077</v>
+        <v>0.706</v>
       </c>
     </row>
     <row r="12">
@@ -764,28 +764,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>S04</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>479.4</v>
+        <v>467.8</v>
       </c>
       <c r="E12" t="n">
-        <v>479.9</v>
+        <v>469.3</v>
       </c>
       <c r="F12" t="n">
-        <v>20.719</v>
+        <v>17.672</v>
       </c>
       <c r="G12" t="n">
-        <v>1.476</v>
+        <v>1.786</v>
       </c>
       <c r="H12" t="n">
-        <v>0.146</v>
+        <v>0.725</v>
       </c>
     </row>
     <row r="13">
@@ -794,28 +794,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>S05</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>480.6</v>
+        <v>477.3</v>
       </c>
       <c r="E13" t="n">
-        <v>481.1</v>
+        <v>478.8</v>
       </c>
       <c r="F13" t="n">
-        <v>19.921</v>
+        <v>19.145</v>
       </c>
       <c r="G13" t="n">
-        <v>1.5</v>
+        <v>1.605</v>
       </c>
       <c r="H13" t="n">
-        <v>0.224</v>
+        <v>0.124</v>
       </c>
     </row>
     <row r="14">
@@ -824,28 +824,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>S03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>492.9</v>
+        <v>479.1</v>
       </c>
       <c r="E14" t="n">
-        <v>493.4</v>
+        <v>480.6</v>
       </c>
       <c r="F14" t="n">
-        <v>23.167</v>
+        <v>13.039</v>
       </c>
       <c r="G14" t="n">
-        <v>1.342</v>
+        <v>1.472</v>
       </c>
       <c r="H14" t="n">
-        <v>0.236</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="15">
@@ -854,28 +854,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>494.3</v>
+        <v>480.7</v>
       </c>
       <c r="E15" t="n">
-        <v>494.8</v>
+        <v>482.2</v>
       </c>
       <c r="F15" t="n">
-        <v>17.666</v>
+        <v>11.784</v>
       </c>
       <c r="G15" t="n">
-        <v>1.491</v>
+        <v>1.848</v>
       </c>
       <c r="H15" t="n">
-        <v>0.315</v>
+        <v>0.601</v>
       </c>
     </row>
     <row r="16">
@@ -884,7 +884,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -893,19 +893,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>507.8</v>
+        <v>493.2</v>
       </c>
       <c r="E16" t="n">
-        <v>508.3</v>
+        <v>493.7</v>
       </c>
       <c r="F16" t="n">
-        <v>32.378</v>
+        <v>27.495</v>
       </c>
       <c r="G16" t="n">
-        <v>1.343</v>
+        <v>1.311</v>
       </c>
       <c r="H16" t="n">
-        <v>0.342</v>
+        <v>0.052</v>
       </c>
     </row>
     <row r="17">
@@ -914,28 +914,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>511.2</v>
+        <v>493.8</v>
       </c>
       <c r="E17" t="n">
-        <v>512.7</v>
+        <v>494.3</v>
       </c>
       <c r="F17" t="n">
-        <v>9.375999999999999</v>
+        <v>18.127</v>
       </c>
       <c r="G17" t="n">
-        <v>1.312</v>
+        <v>1.369</v>
       </c>
       <c r="H17" t="n">
-        <v>0.13</v>
+        <v>0.204</v>
       </c>
     </row>
     <row r="18">
@@ -944,28 +944,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>516.7</v>
+        <v>508.1</v>
       </c>
       <c r="E18" t="n">
-        <v>518.2</v>
+        <v>508.6</v>
       </c>
       <c r="F18" t="n">
-        <v>23.977</v>
+        <v>32.768</v>
       </c>
       <c r="G18" t="n">
-        <v>1.154</v>
+        <v>1.269</v>
       </c>
       <c r="H18" t="n">
-        <v>0.344</v>
+        <v>0.234</v>
       </c>
     </row>
     <row r="19">
@@ -974,7 +974,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -983,19 +983,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>650.3</v>
+        <v>511.2</v>
       </c>
       <c r="E19" t="n">
-        <v>651.8</v>
+        <v>512.7</v>
       </c>
       <c r="F19" t="n">
-        <v>20.912</v>
+        <v>9.375999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>1.187</v>
+        <v>1.312</v>
       </c>
       <c r="H19" t="n">
-        <v>0.27</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="20">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>750.1</v>
+        <v>516.7</v>
       </c>
       <c r="E20" t="n">
-        <v>751.6</v>
+        <v>518.2</v>
       </c>
       <c r="F20" t="n">
-        <v>10.53</v>
+        <v>23.977</v>
       </c>
       <c r="G20" t="n">
-        <v>1.594</v>
+        <v>1.154</v>
       </c>
       <c r="H20" t="n">
-        <v>0.137</v>
+        <v>0.344</v>
       </c>
     </row>
     <row r="21">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1043,19 +1043,49 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>762.3</v>
+        <v>749.2</v>
       </c>
       <c r="E21" t="n">
-        <v>763.8</v>
+        <v>750.7</v>
       </c>
       <c r="F21" t="n">
-        <v>29.836</v>
+        <v>13.767</v>
       </c>
       <c r="G21" t="n">
-        <v>1.662</v>
+        <v>1.498</v>
       </c>
       <c r="H21" t="n">
-        <v>0.152</v>
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>766.2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>767.7</v>
+      </c>
+      <c r="F22" t="n">
+        <v>22.667</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.579</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.29</v>
       </c>
     </row>
   </sheetData>

--- a/xk/output/Q4_最终方案.xlsx
+++ b/xk/output/Q4_最终方案.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,7 +494,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -503,19 +503,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>449.9</v>
+        <v>446.1</v>
       </c>
       <c r="E3" t="n">
-        <v>450.4</v>
+        <v>446.6</v>
       </c>
       <c r="F3" t="n">
-        <v>23.252</v>
+        <v>11.301</v>
       </c>
       <c r="G3" t="n">
-        <v>0.147</v>
+        <v>0.177</v>
       </c>
       <c r="H3" t="n">
-        <v>0.143</v>
+        <v>0.08799999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -524,28 +524,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>S09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>450.7</v>
+        <v>448.2</v>
       </c>
       <c r="E4" t="n">
-        <v>451.2</v>
+        <v>449.7</v>
       </c>
       <c r="F4" t="n">
-        <v>32.195</v>
+        <v>20.61</v>
       </c>
       <c r="G4" t="n">
-        <v>0.216</v>
+        <v>0.152</v>
       </c>
       <c r="H4" t="n">
-        <v>0.213</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="5">
@@ -554,28 +554,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>S04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>452.1</v>
+        <v>449.8</v>
       </c>
       <c r="E5" t="n">
-        <v>452.6</v>
+        <v>451.3</v>
       </c>
       <c r="F5" t="n">
-        <v>30.308</v>
+        <v>19.652</v>
       </c>
       <c r="G5" t="n">
-        <v>0.483</v>
+        <v>0.227</v>
       </c>
       <c r="H5" t="n">
-        <v>0.129</v>
+        <v>0.226</v>
       </c>
     </row>
     <row r="6">
@@ -584,28 +584,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>S08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>453.9</v>
+        <v>451.4</v>
       </c>
       <c r="E6" t="n">
-        <v>454.4</v>
+        <v>452.9</v>
       </c>
       <c r="F6" t="n">
-        <v>27.169</v>
+        <v>10.361</v>
       </c>
       <c r="G6" t="n">
-        <v>0.049</v>
+        <v>0.48</v>
       </c>
       <c r="H6" t="n">
-        <v>0.441</v>
+        <v>0.103</v>
       </c>
     </row>
     <row r="7">
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S06</t>
+          <t>S07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E7" t="n">
-        <v>460.5</v>
+        <v>454.5</v>
       </c>
       <c r="F7" t="n">
-        <v>6.074</v>
+        <v>15.212</v>
       </c>
       <c r="G7" t="n">
-        <v>0.496</v>
+        <v>0.028</v>
       </c>
       <c r="H7" t="n">
-        <v>0.253</v>
+        <v>0.436</v>
       </c>
     </row>
     <row r="8">
@@ -644,28 +644,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>S06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>461.7</v>
+        <v>454.6</v>
       </c>
       <c r="E8" t="n">
-        <v>462.2</v>
+        <v>456.1</v>
       </c>
       <c r="F8" t="n">
-        <v>11.076</v>
+        <v>6.352</v>
       </c>
       <c r="G8" t="n">
-        <v>0.592</v>
+        <v>0.272</v>
       </c>
       <c r="H8" t="n">
-        <v>0.299</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="9">
@@ -674,28 +674,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>S05</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>463.2</v>
+        <v>456.2</v>
       </c>
       <c r="E9" t="n">
-        <v>463.7</v>
+        <v>457.7</v>
       </c>
       <c r="F9" t="n">
-        <v>30.394</v>
+        <v>15.064</v>
       </c>
       <c r="G9" t="n">
-        <v>0.054</v>
+        <v>0.17</v>
       </c>
       <c r="H9" t="n">
-        <v>0.492</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="10">
@@ -704,28 +704,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P15</t>
+          <t>S08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>464.9</v>
+        <v>457.8</v>
       </c>
       <c r="E10" t="n">
-        <v>465.4</v>
+        <v>459.3</v>
       </c>
       <c r="F10" t="n">
-        <v>11.053</v>
+        <v>9.795999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>0.538</v>
+        <v>0.179</v>
       </c>
       <c r="H10" t="n">
-        <v>0.227</v>
+        <v>0.368</v>
       </c>
     </row>
     <row r="11">
@@ -734,28 +734,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P17</t>
+          <t>S04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>466.8</v>
+        <v>459.4</v>
       </c>
       <c r="E11" t="n">
-        <v>467.3</v>
+        <v>460.9</v>
       </c>
       <c r="F11" t="n">
-        <v>28.037</v>
+        <v>19.167</v>
       </c>
       <c r="G11" t="n">
-        <v>0.051</v>
+        <v>0.589</v>
       </c>
       <c r="H11" t="n">
-        <v>0.706</v>
+        <v>0.253</v>
       </c>
     </row>
     <row r="12">
@@ -764,7 +764,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>S04</t>
+          <t>S08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -773,19 +773,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>467.8</v>
+        <v>461</v>
       </c>
       <c r="E12" t="n">
-        <v>469.3</v>
+        <v>462.5</v>
       </c>
       <c r="F12" t="n">
-        <v>17.672</v>
+        <v>10.363</v>
       </c>
       <c r="G12" t="n">
-        <v>1.786</v>
+        <v>0.492</v>
       </c>
       <c r="H12" t="n">
-        <v>0.725</v>
+        <v>0.395</v>
       </c>
     </row>
     <row r="13">
@@ -794,7 +794,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>S09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>477.3</v>
+        <v>462.6</v>
       </c>
       <c r="E13" t="n">
-        <v>478.8</v>
+        <v>464.1</v>
       </c>
       <c r="F13" t="n">
-        <v>19.145</v>
+        <v>20.998</v>
       </c>
       <c r="G13" t="n">
-        <v>1.605</v>
+        <v>0.23</v>
       </c>
       <c r="H13" t="n">
-        <v>0.124</v>
+        <v>0.452</v>
       </c>
     </row>
     <row r="14">
@@ -824,7 +824,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S05</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -833,19 +833,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>479.1</v>
+        <v>464.2</v>
       </c>
       <c r="E14" t="n">
-        <v>480.6</v>
+        <v>465.7</v>
       </c>
       <c r="F14" t="n">
-        <v>13.039</v>
+        <v>14.076</v>
       </c>
       <c r="G14" t="n">
-        <v>1.472</v>
+        <v>0.516</v>
       </c>
       <c r="H14" t="n">
-        <v>0.012</v>
+        <v>0.274</v>
       </c>
     </row>
     <row r="15">
@@ -854,7 +854,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>480.7</v>
+        <v>465.8</v>
       </c>
       <c r="E15" t="n">
-        <v>482.2</v>
+        <v>467.3</v>
       </c>
       <c r="F15" t="n">
-        <v>11.784</v>
+        <v>13.9</v>
       </c>
       <c r="G15" t="n">
-        <v>1.848</v>
+        <v>0.051</v>
       </c>
       <c r="H15" t="n">
-        <v>0.601</v>
+        <v>0.706</v>
       </c>
     </row>
     <row r="16">
@@ -884,28 +884,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>S07</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>493.2</v>
+        <v>467.4</v>
       </c>
       <c r="E16" t="n">
-        <v>493.7</v>
+        <v>468.9</v>
       </c>
       <c r="F16" t="n">
-        <v>27.495</v>
+        <v>14.275</v>
       </c>
       <c r="G16" t="n">
-        <v>1.311</v>
+        <v>1.429</v>
       </c>
       <c r="H16" t="n">
-        <v>0.052</v>
+        <v>0.982</v>
       </c>
     </row>
     <row r="17">
@@ -914,28 +914,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>493.8</v>
+        <v>477.3</v>
       </c>
       <c r="E17" t="n">
-        <v>494.3</v>
+        <v>478.8</v>
       </c>
       <c r="F17" t="n">
-        <v>18.127</v>
+        <v>7.787</v>
       </c>
       <c r="G17" t="n">
-        <v>1.369</v>
+        <v>1.605</v>
       </c>
       <c r="H17" t="n">
-        <v>0.204</v>
+        <v>0.124</v>
       </c>
     </row>
     <row r="18">
@@ -944,28 +944,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>508.1</v>
+        <v>478.9</v>
       </c>
       <c r="E18" t="n">
-        <v>508.6</v>
+        <v>480.4</v>
       </c>
       <c r="F18" t="n">
-        <v>32.768</v>
+        <v>14.024</v>
       </c>
       <c r="G18" t="n">
-        <v>1.269</v>
+        <v>1.47</v>
       </c>
       <c r="H18" t="n">
-        <v>0.234</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="19">
@@ -974,7 +974,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -983,19 +983,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>511.2</v>
+        <v>480.5</v>
       </c>
       <c r="E19" t="n">
-        <v>512.7</v>
+        <v>482</v>
       </c>
       <c r="F19" t="n">
-        <v>9.375999999999999</v>
+        <v>12.03</v>
       </c>
       <c r="G19" t="n">
-        <v>1.312</v>
+        <v>1.73</v>
       </c>
       <c r="H19" t="n">
-        <v>0.13</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="20">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>516.7</v>
+        <v>492</v>
       </c>
       <c r="E20" t="n">
-        <v>518.2</v>
+        <v>493.5</v>
       </c>
       <c r="F20" t="n">
-        <v>23.977</v>
+        <v>23.861</v>
       </c>
       <c r="G20" t="n">
-        <v>1.154</v>
+        <v>1.325</v>
       </c>
       <c r="H20" t="n">
-        <v>0.344</v>
+        <v>0.151</v>
       </c>
     </row>
     <row r="21">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1043,19 +1043,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>749.2</v>
+        <v>493.6</v>
       </c>
       <c r="E21" t="n">
-        <v>750.7</v>
+        <v>495.1</v>
       </c>
       <c r="F21" t="n">
-        <v>13.767</v>
+        <v>25.095</v>
       </c>
       <c r="G21" t="n">
-        <v>1.498</v>
+        <v>1.618</v>
       </c>
       <c r="H21" t="n">
-        <v>0.11</v>
+        <v>0.5610000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1064,28 +1064,358 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>拍照</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>508.1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>508.6</v>
+      </c>
+      <c r="F22" t="n">
+        <v>32.768</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.269</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.234</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>516.4</v>
+      </c>
+      <c r="E23" t="n">
+        <v>517.9</v>
+      </c>
+      <c r="F23" t="n">
+        <v>23.994</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.302</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>518</v>
+      </c>
+      <c r="E24" t="n">
+        <v>519.5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>24.227</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.372</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.179</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>S11</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>射击</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>766.2</v>
-      </c>
-      <c r="E22" t="n">
-        <v>767.7</v>
-      </c>
-      <c r="F22" t="n">
-        <v>22.667</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1.579</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.29</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>521.2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>522.7</v>
+      </c>
+      <c r="F25" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.393</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>526</v>
+      </c>
+      <c r="E26" t="n">
+        <v>527.5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>28.42</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.476</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.267</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>532.4</v>
+      </c>
+      <c r="E27" t="n">
+        <v>533.9</v>
+      </c>
+      <c r="F27" t="n">
+        <v>25.428</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.103</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>534</v>
+      </c>
+      <c r="E28" t="n">
+        <v>535.5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>26.912</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.415</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.271</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>535.6</v>
+      </c>
+      <c r="E29" t="n">
+        <v>537.1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>28.745</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.563</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.282</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>749.2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>750.7</v>
+      </c>
+      <c r="F30" t="n">
+        <v>23.169</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.498</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>750.8</v>
+      </c>
+      <c r="E31" t="n">
+        <v>752.3</v>
+      </c>
+      <c r="F31" t="n">
+        <v>24.899</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.748</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.251</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>771</v>
+      </c>
+      <c r="E32" t="n">
+        <v>772.5</v>
+      </c>
+      <c r="F32" t="n">
+        <v>25.64</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.268</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>811</v>
+      </c>
+      <c r="E33" t="n">
+        <v>812.5</v>
+      </c>
+      <c r="F33" t="n">
+        <v>24.217</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.578</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.188</v>
       </c>
     </row>
   </sheetData>

--- a/xk/output/Q4_最终方案.xlsx
+++ b/xk/output/Q4_最终方案.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,28 +494,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P15</t>
+          <t>S08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>446.1</v>
+        <v>446.5</v>
       </c>
       <c r="E3" t="n">
-        <v>446.6</v>
+        <v>448</v>
       </c>
       <c r="F3" t="n">
-        <v>11.301</v>
+        <v>9.706</v>
       </c>
       <c r="G3" t="n">
-        <v>0.177</v>
+        <v>0.014</v>
       </c>
       <c r="H3" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="4">
@@ -524,7 +524,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S09</t>
+          <t>S08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -533,19 +533,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>448.2</v>
+        <v>448</v>
       </c>
       <c r="E4" t="n">
-        <v>449.7</v>
+        <v>449.5</v>
       </c>
       <c r="F4" t="n">
-        <v>20.61</v>
+        <v>9.672000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>0.152</v>
+        <v>0.149</v>
       </c>
       <c r="H4" t="n">
-        <v>0.115</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="5">
@@ -554,7 +554,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S04</t>
+          <t>S08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -563,19 +563,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>449.8</v>
+        <v>449.5</v>
       </c>
       <c r="E5" t="n">
-        <v>451.3</v>
+        <v>451</v>
       </c>
       <c r="F5" t="n">
-        <v>19.652</v>
+        <v>9.83</v>
       </c>
       <c r="G5" t="n">
-        <v>0.227</v>
+        <v>0.198</v>
       </c>
       <c r="H5" t="n">
-        <v>0.226</v>
+        <v>0.183</v>
       </c>
     </row>
     <row r="6">
@@ -584,7 +584,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S08</t>
+          <t>S07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>451.4</v>
+        <v>451</v>
       </c>
       <c r="E6" t="n">
-        <v>452.9</v>
+        <v>452.5</v>
       </c>
       <c r="F6" t="n">
-        <v>10.361</v>
+        <v>15.414</v>
       </c>
       <c r="G6" t="n">
-        <v>0.48</v>
+        <v>0.473</v>
       </c>
       <c r="H6" t="n">
-        <v>0.103</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="7">
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>453</v>
+        <v>452.5</v>
       </c>
       <c r="E7" t="n">
-        <v>454.5</v>
+        <v>454</v>
       </c>
       <c r="F7" t="n">
-        <v>15.212</v>
+        <v>15.235</v>
       </c>
       <c r="G7" t="n">
-        <v>0.028</v>
+        <v>0.214</v>
       </c>
       <c r="H7" t="n">
-        <v>0.436</v>
+        <v>0.395</v>
       </c>
     </row>
     <row r="8">
@@ -644,7 +644,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>S06</t>
+          <t>S09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>454.6</v>
+        <v>454</v>
       </c>
       <c r="E8" t="n">
-        <v>456.1</v>
+        <v>455.5</v>
       </c>
       <c r="F8" t="n">
-        <v>6.352</v>
+        <v>21.33</v>
       </c>
       <c r="G8" t="n">
-        <v>0.272</v>
+        <v>0.28</v>
       </c>
       <c r="H8" t="n">
-        <v>0.115</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="9">
@@ -674,7 +674,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>S09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -683,19 +683,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>456.2</v>
+        <v>455.5</v>
       </c>
       <c r="E9" t="n">
-        <v>457.7</v>
+        <v>457</v>
       </c>
       <c r="F9" t="n">
-        <v>15.064</v>
+        <v>21.013</v>
       </c>
       <c r="G9" t="n">
-        <v>0.17</v>
+        <v>0.201</v>
       </c>
       <c r="H9" t="n">
-        <v>0.105</v>
+        <v>0.147</v>
       </c>
     </row>
     <row r="10">
@@ -704,7 +704,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S08</t>
+          <t>S04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -713,19 +713,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>457.8</v>
+        <v>457</v>
       </c>
       <c r="E10" t="n">
-        <v>459.3</v>
+        <v>458.5</v>
       </c>
       <c r="F10" t="n">
-        <v>9.795999999999999</v>
+        <v>19.405</v>
       </c>
       <c r="G10" t="n">
-        <v>0.179</v>
+        <v>0.158</v>
       </c>
       <c r="H10" t="n">
-        <v>0.368</v>
+        <v>0.082</v>
       </c>
     </row>
     <row r="11">
@@ -734,7 +734,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S04</t>
+          <t>S06</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -743,19 +743,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>459.4</v>
+        <v>458.5</v>
       </c>
       <c r="E11" t="n">
-        <v>460.9</v>
+        <v>460</v>
       </c>
       <c r="F11" t="n">
-        <v>19.167</v>
+        <v>6.289</v>
       </c>
       <c r="G11" t="n">
-        <v>0.589</v>
+        <v>0.372</v>
       </c>
       <c r="H11" t="n">
-        <v>0.253</v>
+        <v>0.298</v>
       </c>
     </row>
     <row r="12">
@@ -764,7 +764,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>S08</t>
+          <t>S05</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -773,19 +773,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E12" t="n">
-        <v>462.5</v>
+        <v>461.5</v>
       </c>
       <c r="F12" t="n">
-        <v>10.363</v>
+        <v>14.213</v>
       </c>
       <c r="G12" t="n">
-        <v>0.492</v>
+        <v>0.673</v>
       </c>
       <c r="H12" t="n">
-        <v>0.395</v>
+        <v>0.118</v>
       </c>
     </row>
     <row r="13">
@@ -794,7 +794,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>S09</t>
+          <t>S05</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>462.6</v>
+        <v>461.5</v>
       </c>
       <c r="E13" t="n">
-        <v>464.1</v>
+        <v>463</v>
       </c>
       <c r="F13" t="n">
-        <v>20.998</v>
+        <v>13.405</v>
       </c>
       <c r="G13" t="n">
-        <v>0.23</v>
+        <v>0.282</v>
       </c>
       <c r="H13" t="n">
-        <v>0.452</v>
+        <v>0.432</v>
       </c>
     </row>
     <row r="14">
@@ -824,7 +824,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>S09</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -833,19 +833,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>464.2</v>
+        <v>463</v>
       </c>
       <c r="E14" t="n">
-        <v>465.7</v>
+        <v>464.5</v>
       </c>
       <c r="F14" t="n">
-        <v>14.076</v>
+        <v>20.951</v>
       </c>
       <c r="G14" t="n">
-        <v>0.516</v>
+        <v>0.384</v>
       </c>
       <c r="H14" t="n">
-        <v>0.274</v>
+        <v>0.329</v>
       </c>
     </row>
     <row r="15">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>465.8</v>
+        <v>464.5</v>
       </c>
       <c r="E15" t="n">
-        <v>467.3</v>
+        <v>466</v>
       </c>
       <c r="F15" t="n">
-        <v>13.9</v>
+        <v>13.992</v>
       </c>
       <c r="G15" t="n">
-        <v>0.051</v>
+        <v>0.47</v>
       </c>
       <c r="H15" t="n">
-        <v>0.706</v>
+        <v>0.252</v>
       </c>
     </row>
     <row r="16">
@@ -884,7 +884,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>S07</t>
+          <t>S05</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -893,19 +893,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>467.4</v>
+        <v>466</v>
       </c>
       <c r="E16" t="n">
-        <v>468.9</v>
+        <v>467.5</v>
       </c>
       <c r="F16" t="n">
-        <v>14.275</v>
+        <v>14.474</v>
       </c>
       <c r="G16" t="n">
-        <v>1.429</v>
+        <v>0.173</v>
       </c>
       <c r="H16" t="n">
-        <v>0.982</v>
+        <v>0.777</v>
       </c>
     </row>
     <row r="17">
@@ -914,7 +914,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -923,19 +923,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>477.3</v>
+        <v>468.1</v>
       </c>
       <c r="E17" t="n">
-        <v>478.8</v>
+        <v>469.6</v>
       </c>
       <c r="F17" t="n">
-        <v>7.787</v>
+        <v>27.972</v>
       </c>
       <c r="G17" t="n">
-        <v>1.605</v>
+        <v>1.976</v>
       </c>
       <c r="H17" t="n">
-        <v>0.124</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="18">
@@ -944,7 +944,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -953,19 +953,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>478.9</v>
+        <v>477</v>
       </c>
       <c r="E18" t="n">
-        <v>480.4</v>
+        <v>478.5</v>
       </c>
       <c r="F18" t="n">
-        <v>14.024</v>
+        <v>8.212</v>
       </c>
       <c r="G18" t="n">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="H18" t="n">
-        <v>0.065</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="19">
@@ -974,28 +974,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>480.5</v>
+        <v>479.4</v>
       </c>
       <c r="E19" t="n">
-        <v>482</v>
+        <v>479.9</v>
       </c>
       <c r="F19" t="n">
-        <v>12.03</v>
+        <v>20.719</v>
       </c>
       <c r="G19" t="n">
-        <v>1.73</v>
+        <v>1.476</v>
       </c>
       <c r="H19" t="n">
-        <v>0.63</v>
+        <v>0.146</v>
       </c>
     </row>
     <row r="20">
@@ -1004,28 +1004,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>492</v>
+        <v>479.9</v>
       </c>
       <c r="E20" t="n">
-        <v>493.5</v>
+        <v>480.4</v>
       </c>
       <c r="F20" t="n">
-        <v>23.861</v>
+        <v>34.71</v>
       </c>
       <c r="G20" t="n">
-        <v>1.325</v>
+        <v>1.47</v>
       </c>
       <c r="H20" t="n">
-        <v>0.151</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="21">
@@ -1043,19 +1043,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>493.6</v>
+        <v>491.8</v>
       </c>
       <c r="E21" t="n">
-        <v>495.1</v>
+        <v>493.3</v>
       </c>
       <c r="F21" t="n">
-        <v>25.095</v>
+        <v>23.724</v>
       </c>
       <c r="G21" t="n">
-        <v>1.618</v>
+        <v>1.364</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.292</v>
       </c>
     </row>
     <row r="22">
@@ -1064,28 +1064,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>508.1</v>
+        <v>493.3</v>
       </c>
       <c r="E22" t="n">
-        <v>508.6</v>
+        <v>494.8</v>
       </c>
       <c r="F22" t="n">
-        <v>32.768</v>
+        <v>24.685</v>
       </c>
       <c r="G22" t="n">
-        <v>1.269</v>
+        <v>1.491</v>
       </c>
       <c r="H22" t="n">
-        <v>0.234</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="23">
@@ -1094,28 +1094,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>516.4</v>
+        <v>507.8</v>
       </c>
       <c r="E23" t="n">
-        <v>517.9</v>
+        <v>508.3</v>
       </c>
       <c r="F23" t="n">
-        <v>23.994</v>
+        <v>32.378</v>
       </c>
       <c r="G23" t="n">
-        <v>1.111</v>
+        <v>1.343</v>
       </c>
       <c r="H23" t="n">
-        <v>0.302</v>
+        <v>0.342</v>
       </c>
     </row>
     <row r="24">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1133,19 +1133,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>518</v>
+        <v>509.4</v>
       </c>
       <c r="E24" t="n">
-        <v>519.5</v>
+        <v>510.9</v>
       </c>
       <c r="F24" t="n">
-        <v>24.227</v>
+        <v>17.344</v>
       </c>
       <c r="G24" t="n">
-        <v>1.372</v>
+        <v>1.098</v>
       </c>
       <c r="H24" t="n">
-        <v>0.179</v>
+        <v>0.262</v>
       </c>
     </row>
     <row r="25">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1163,19 +1163,19 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>521.2</v>
+        <v>513.9</v>
       </c>
       <c r="E25" t="n">
-        <v>522.7</v>
+        <v>515.4</v>
       </c>
       <c r="F25" t="n">
-        <v>24.86</v>
+        <v>24.864</v>
       </c>
       <c r="G25" t="n">
-        <v>0.76</v>
+        <v>1.262</v>
       </c>
       <c r="H25" t="n">
-        <v>0.393</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="26">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1193,19 +1193,19 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>526</v>
+        <v>516.9</v>
       </c>
       <c r="E26" t="n">
-        <v>527.5</v>
+        <v>518.4</v>
       </c>
       <c r="F26" t="n">
-        <v>28.42</v>
+        <v>23.984</v>
       </c>
       <c r="G26" t="n">
-        <v>1.476</v>
+        <v>1.187</v>
       </c>
       <c r="H26" t="n">
-        <v>0.267</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="27">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>532.4</v>
+        <v>533.4</v>
       </c>
       <c r="E27" t="n">
-        <v>533.9</v>
+        <v>534.9</v>
       </c>
       <c r="F27" t="n">
-        <v>25.428</v>
+        <v>26.298</v>
       </c>
       <c r="G27" t="n">
-        <v>0.984</v>
+        <v>1.191</v>
       </c>
       <c r="H27" t="n">
-        <v>0.103</v>
+        <v>0.365</v>
       </c>
     </row>
     <row r="28">
@@ -1253,19 +1253,19 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>534</v>
+        <v>534.9</v>
       </c>
       <c r="E28" t="n">
-        <v>535.5</v>
+        <v>536.4</v>
       </c>
       <c r="F28" t="n">
-        <v>26.912</v>
+        <v>27.925</v>
       </c>
       <c r="G28" t="n">
-        <v>1.415</v>
+        <v>1.603</v>
       </c>
       <c r="H28" t="n">
-        <v>0.271</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="29">
@@ -1283,19 +1283,19 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>535.6</v>
+        <v>536.4</v>
       </c>
       <c r="E29" t="n">
-        <v>537.1</v>
+        <v>537.9</v>
       </c>
       <c r="F29" t="n">
-        <v>28.745</v>
+        <v>29.624</v>
       </c>
       <c r="G29" t="n">
-        <v>1.563</v>
+        <v>1.335</v>
       </c>
       <c r="H29" t="n">
-        <v>0.282</v>
+        <v>0.395</v>
       </c>
     </row>
     <row r="30">
@@ -1313,19 +1313,19 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>749.2</v>
+        <v>748.8</v>
       </c>
       <c r="E30" t="n">
-        <v>750.7</v>
+        <v>750.3</v>
       </c>
       <c r="F30" t="n">
-        <v>23.169</v>
+        <v>22.819</v>
       </c>
       <c r="G30" t="n">
-        <v>1.498</v>
+        <v>1.529</v>
       </c>
       <c r="H30" t="n">
-        <v>0.11</v>
+        <v>0.184</v>
       </c>
     </row>
     <row r="31">
@@ -1343,19 +1343,19 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>750.8</v>
+        <v>750.3</v>
       </c>
       <c r="E31" t="n">
-        <v>752.3</v>
+        <v>751.8</v>
       </c>
       <c r="F31" t="n">
-        <v>24.899</v>
+        <v>24.291</v>
       </c>
       <c r="G31" t="n">
-        <v>1.748</v>
+        <v>1.624</v>
       </c>
       <c r="H31" t="n">
-        <v>0.251</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="32">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1373,19 +1373,19 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>771</v>
+        <v>751.8</v>
       </c>
       <c r="E32" t="n">
-        <v>772.5</v>
+        <v>753.3</v>
       </c>
       <c r="F32" t="n">
-        <v>25.64</v>
+        <v>26.35</v>
       </c>
       <c r="G32" t="n">
-        <v>0.403</v>
+        <v>1.962</v>
       </c>
       <c r="H32" t="n">
-        <v>0.268</v>
+        <v>0.248</v>
       </c>
     </row>
     <row r="33">
@@ -1394,28 +1394,118 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>762.3</v>
+      </c>
+      <c r="E33" t="n">
+        <v>763.8</v>
+      </c>
+      <c r="F33" t="n">
+        <v>29.836</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.662</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.152</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>S11</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>射击</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>811</v>
-      </c>
-      <c r="E33" t="n">
-        <v>812.5</v>
-      </c>
-      <c r="F33" t="n">
-        <v>24.217</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.578</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.188</v>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>769.8</v>
+      </c>
+      <c r="E34" t="n">
+        <v>771.3</v>
+      </c>
+      <c r="F34" t="n">
+        <v>25.195</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.412</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>789.3</v>
+      </c>
+      <c r="E35" t="n">
+        <v>790.8</v>
+      </c>
+      <c r="F35" t="n">
+        <v>26.179</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.417</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>793.8</v>
+      </c>
+      <c r="E36" t="n">
+        <v>795.3</v>
+      </c>
+      <c r="F36" t="n">
+        <v>26.603</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.238</v>
       </c>
     </row>
   </sheetData>

--- a/xk/output/Q4_最终方案.xlsx
+++ b/xk/output/Q4_最终方案.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,7 +494,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>S08</t>
+          <t>S06</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -509,7 +509,7 @@
         <v>448</v>
       </c>
       <c r="F3" t="n">
-        <v>9.706</v>
+        <v>6.765</v>
       </c>
       <c r="G3" t="n">
         <v>0.014</v>
@@ -524,7 +524,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S08</t>
+          <t>S07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -539,7 +539,7 @@
         <v>449.5</v>
       </c>
       <c r="F4" t="n">
-        <v>9.672000000000001</v>
+        <v>15.172</v>
       </c>
       <c r="G4" t="n">
         <v>0.149</v>
@@ -614,7 +614,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S07</t>
+          <t>S04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -629,7 +629,7 @@
         <v>454</v>
       </c>
       <c r="F7" t="n">
-        <v>15.235</v>
+        <v>18.691</v>
       </c>
       <c r="G7" t="n">
         <v>0.214</v>
@@ -644,7 +644,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>S09</t>
+          <t>S06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -659,7 +659,7 @@
         <v>455.5</v>
       </c>
       <c r="F8" t="n">
-        <v>21.33</v>
+        <v>6.237</v>
       </c>
       <c r="G8" t="n">
         <v>0.28</v>
@@ -674,7 +674,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S09</t>
+          <t>S05</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -689,7 +689,7 @@
         <v>457</v>
       </c>
       <c r="F9" t="n">
-        <v>21.013</v>
+        <v>15.033</v>
       </c>
       <c r="G9" t="n">
         <v>0.201</v>
@@ -734,7 +734,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S06</t>
+          <t>S09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -749,7 +749,7 @@
         <v>460</v>
       </c>
       <c r="F11" t="n">
-        <v>6.289</v>
+        <v>20.591</v>
       </c>
       <c r="G11" t="n">
         <v>0.372</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>S08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -779,7 +779,7 @@
         <v>461.5</v>
       </c>
       <c r="F12" t="n">
-        <v>14.213</v>
+        <v>10.025</v>
       </c>
       <c r="G12" t="n">
         <v>0.673</v>
@@ -824,7 +824,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>S09</t>
+          <t>S07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -839,7 +839,7 @@
         <v>464.5</v>
       </c>
       <c r="F14" t="n">
-        <v>20.951</v>
+        <v>13.839</v>
       </c>
       <c r="G14" t="n">
         <v>0.384</v>
@@ -854,7 +854,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>S07</t>
+          <t>S04</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -869,7 +869,7 @@
         <v>466</v>
       </c>
       <c r="F15" t="n">
-        <v>13.992</v>
+        <v>19.001</v>
       </c>
       <c r="G15" t="n">
         <v>0.47</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>S06</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -893,19 +893,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>466</v>
+        <v>466.5</v>
       </c>
       <c r="E16" t="n">
-        <v>467.5</v>
+        <v>468</v>
       </c>
       <c r="F16" t="n">
-        <v>14.474</v>
+        <v>5.532</v>
       </c>
       <c r="G16" t="n">
-        <v>0.173</v>
+        <v>0.578</v>
       </c>
       <c r="H16" t="n">
-        <v>0.777</v>
+        <v>0.847</v>
       </c>
     </row>
     <row r="17">
@@ -944,7 +944,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -959,7 +959,7 @@
         <v>478.5</v>
       </c>
       <c r="F18" t="n">
-        <v>8.212</v>
+        <v>16.487</v>
       </c>
       <c r="G18" t="n">
         <v>1.63</v>
@@ -1034,28 +1034,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>491.8</v>
+        <v>492.9</v>
       </c>
       <c r="E21" t="n">
-        <v>493.3</v>
+        <v>493.4</v>
       </c>
       <c r="F21" t="n">
-        <v>23.724</v>
+        <v>18.95</v>
       </c>
       <c r="G21" t="n">
-        <v>1.364</v>
+        <v>1.342</v>
       </c>
       <c r="H21" t="n">
-        <v>0.292</v>
+        <v>0.236</v>
       </c>
     </row>
     <row r="22">
@@ -1064,28 +1064,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>493.3</v>
+        <v>507.8</v>
       </c>
       <c r="E22" t="n">
-        <v>494.8</v>
+        <v>508.3</v>
       </c>
       <c r="F22" t="n">
-        <v>24.685</v>
+        <v>32.378</v>
       </c>
       <c r="G22" t="n">
-        <v>1.491</v>
+        <v>1.343</v>
       </c>
       <c r="H22" t="n">
-        <v>0.315</v>
+        <v>0.342</v>
       </c>
     </row>
     <row r="23">
@@ -1094,28 +1094,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>507.8</v>
+        <v>533.4</v>
       </c>
       <c r="E23" t="n">
-        <v>508.3</v>
+        <v>534.9</v>
       </c>
       <c r="F23" t="n">
-        <v>32.378</v>
+        <v>26.298</v>
       </c>
       <c r="G23" t="n">
-        <v>1.343</v>
+        <v>1.191</v>
       </c>
       <c r="H23" t="n">
-        <v>0.342</v>
+        <v>0.365</v>
       </c>
     </row>
     <row r="24">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1133,19 +1133,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>509.4</v>
+        <v>534.9</v>
       </c>
       <c r="E24" t="n">
-        <v>510.9</v>
+        <v>536.4</v>
       </c>
       <c r="F24" t="n">
-        <v>17.344</v>
+        <v>27.925</v>
       </c>
       <c r="G24" t="n">
-        <v>1.098</v>
+        <v>1.603</v>
       </c>
       <c r="H24" t="n">
-        <v>0.262</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="25">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1163,19 +1163,19 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>513.9</v>
+        <v>536.4</v>
       </c>
       <c r="E25" t="n">
-        <v>515.4</v>
+        <v>537.9</v>
       </c>
       <c r="F25" t="n">
-        <v>24.864</v>
+        <v>29.624</v>
       </c>
       <c r="G25" t="n">
-        <v>1.262</v>
+        <v>1.335</v>
       </c>
       <c r="H25" t="n">
-        <v>0.098</v>
+        <v>0.395</v>
       </c>
     </row>
     <row r="26">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1193,19 +1193,19 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>516.9</v>
+        <v>748.8</v>
       </c>
       <c r="E26" t="n">
-        <v>518.4</v>
+        <v>750.3</v>
       </c>
       <c r="F26" t="n">
-        <v>23.984</v>
+        <v>22.819</v>
       </c>
       <c r="G26" t="n">
-        <v>1.187</v>
+        <v>1.529</v>
       </c>
       <c r="H26" t="n">
-        <v>0.29</v>
+        <v>0.184</v>
       </c>
     </row>
     <row r="27">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>533.4</v>
+        <v>750.3</v>
       </c>
       <c r="E27" t="n">
-        <v>534.9</v>
+        <v>751.8</v>
       </c>
       <c r="F27" t="n">
-        <v>26.298</v>
+        <v>15.202</v>
       </c>
       <c r="G27" t="n">
-        <v>1.191</v>
+        <v>1.624</v>
       </c>
       <c r="H27" t="n">
-        <v>0.365</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="28">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S14</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1253,19 +1253,19 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>534.9</v>
+        <v>751.8</v>
       </c>
       <c r="E28" t="n">
-        <v>536.4</v>
+        <v>753.3</v>
       </c>
       <c r="F28" t="n">
-        <v>27.925</v>
+        <v>11.114</v>
       </c>
       <c r="G28" t="n">
-        <v>1.603</v>
+        <v>1.962</v>
       </c>
       <c r="H28" t="n">
-        <v>0.135</v>
+        <v>0.248</v>
       </c>
     </row>
     <row r="29">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1283,19 +1283,19 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>536.4</v>
+        <v>762.3</v>
       </c>
       <c r="E29" t="n">
-        <v>537.9</v>
+        <v>763.8</v>
       </c>
       <c r="F29" t="n">
-        <v>29.624</v>
+        <v>29.836</v>
       </c>
       <c r="G29" t="n">
-        <v>1.335</v>
+        <v>1.662</v>
       </c>
       <c r="H29" t="n">
-        <v>0.395</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="30">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1313,19 +1313,19 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>748.8</v>
+        <v>778.8</v>
       </c>
       <c r="E30" t="n">
-        <v>750.3</v>
+        <v>780.3</v>
       </c>
       <c r="F30" t="n">
-        <v>22.819</v>
+        <v>23.609</v>
       </c>
       <c r="G30" t="n">
-        <v>1.529</v>
+        <v>0.479</v>
       </c>
       <c r="H30" t="n">
-        <v>0.184</v>
+        <v>0.127</v>
       </c>
     </row>
     <row r="31">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1343,19 +1343,19 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>750.3</v>
+        <v>784.8</v>
       </c>
       <c r="E31" t="n">
-        <v>751.8</v>
+        <v>786.3</v>
       </c>
       <c r="F31" t="n">
-        <v>24.291</v>
+        <v>24.04</v>
       </c>
       <c r="G31" t="n">
-        <v>1.624</v>
+        <v>0.265</v>
       </c>
       <c r="H31" t="n">
-        <v>0.181</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="32">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1373,19 +1373,19 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>751.8</v>
+        <v>793.8</v>
       </c>
       <c r="E32" t="n">
-        <v>753.3</v>
+        <v>795.3</v>
       </c>
       <c r="F32" t="n">
-        <v>26.35</v>
+        <v>26.603</v>
       </c>
       <c r="G32" t="n">
-        <v>1.962</v>
+        <v>0.218</v>
       </c>
       <c r="H32" t="n">
-        <v>0.248</v>
+        <v>0.238</v>
       </c>
     </row>
     <row r="33">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1403,19 +1403,19 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>762.3</v>
+        <v>796.8</v>
       </c>
       <c r="E33" t="n">
-        <v>763.8</v>
+        <v>798.3</v>
       </c>
       <c r="F33" t="n">
-        <v>29.836</v>
+        <v>26.31</v>
       </c>
       <c r="G33" t="n">
-        <v>1.662</v>
+        <v>0.141</v>
       </c>
       <c r="H33" t="n">
-        <v>0.152</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="34">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>769.8</v>
+        <v>799.8</v>
       </c>
       <c r="E34" t="n">
-        <v>771.3</v>
+        <v>801.3</v>
       </c>
       <c r="F34" t="n">
-        <v>25.195</v>
+        <v>25.449</v>
       </c>
       <c r="G34" t="n">
-        <v>0.113</v>
+        <v>0.487</v>
       </c>
       <c r="H34" t="n">
-        <v>0.412</v>
+        <v>0.195</v>
       </c>
     </row>
     <row r="35">
@@ -1463,49 +1463,19 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>789.3</v>
+        <v>807.3</v>
       </c>
       <c r="E35" t="n">
-        <v>790.8</v>
+        <v>808.8</v>
       </c>
       <c r="F35" t="n">
-        <v>26.179</v>
+        <v>22.884</v>
       </c>
       <c r="G35" t="n">
-        <v>0.253</v>
+        <v>0.353</v>
       </c>
       <c r="H35" t="n">
-        <v>0.417</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>射击</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>793.8</v>
-      </c>
-      <c r="E36" t="n">
-        <v>795.3</v>
-      </c>
-      <c r="F36" t="n">
-        <v>26.603</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.218</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.238</v>
+        <v>0.285</v>
       </c>
     </row>
   </sheetData>
